--- a/excel-files/TAGUIG_PATEROS/PAULINA MANALO ES.xlsx
+++ b/excel-files/TAGUIG_PATEROS/PAULINA MANALO ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1514BB29-FE2E-45FE-B418-B611CDBE9188}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A67DB40F-DE62-4300-9C0C-380BDFC3D48C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5716,24 +5716,26 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>107</v>
+      </c>
       <c r="D5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
@@ -5741,14 +5743,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" ref="O5" si="5">IF((K5-J5)&lt;0,0,(K5-J5))</f>
@@ -5756,14 +5758,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" ref="T5" si="6">IF((P5-Q5)&lt;0,0,(P5-Q5))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" ref="U5" si="7">IF((Q5-P5)&lt;0,0,(Q5-P5))</f>
@@ -5771,38 +5773,40 @@
       </c>
       <c r="V5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" ref="Z5" si="8">IF((V5-W5)&lt;0,0,(V5-W5))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" ref="AA5" si="9">IF((W5-V5)&lt;0,0,(W5-V5))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>107</v>
+      </c>
       <c r="D6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="3"/>
@@ -5810,14 +5814,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
@@ -5825,14 +5829,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
@@ -5840,38 +5844,40 @@
       </c>
       <c r="V6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>107</v>
+      </c>
       <c r="D7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="3"/>
@@ -5879,14 +5885,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="11"/>
@@ -5894,14 +5900,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="13"/>
@@ -5909,38 +5915,40 @@
       </c>
       <c r="V7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>107</v>
+      </c>
       <c r="D8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="3"/>
@@ -5948,14 +5956,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="11"/>
@@ -5963,14 +5971,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="13"/>
@@ -5978,38 +5986,40 @@
       </c>
       <c r="V8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>107</v>
+      </c>
       <c r="D9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="3"/>
@@ -6017,14 +6027,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="11"/>
@@ -6032,14 +6042,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="13"/>
@@ -6047,38 +6057,40 @@
       </c>
       <c r="V9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>107</v>
+      </c>
       <c r="D10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -6086,14 +6098,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="11"/>
@@ -6101,14 +6113,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="13"/>
@@ -6116,38 +6128,40 @@
       </c>
       <c r="V10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>107</v>
+      </c>
       <c r="D11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
@@ -6155,14 +6169,14 @@
       </c>
       <c r="J11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="11"/>
@@ -6170,14 +6184,14 @@
       </c>
       <c r="P11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="13"/>
@@ -6185,38 +6199,40 @@
       </c>
       <c r="V11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>107</v>
+      </c>
       <c r="D12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
@@ -6224,14 +6240,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="11"/>
@@ -6239,14 +6255,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="13"/>
@@ -6254,14 +6270,14 @@
       </c>
       <c r="V12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="15"/>
@@ -6281,24 +6297,26 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>119</v>
+      </c>
       <c r="D14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
@@ -6306,14 +6324,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="11"/>
@@ -6321,14 +6339,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="13"/>
@@ -6336,38 +6354,40 @@
       </c>
       <c r="V14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>119</v>
+      </c>
       <c r="D15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="3"/>
@@ -6375,14 +6395,14 @@
       </c>
       <c r="J15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="11"/>
@@ -6390,14 +6410,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="13"/>
@@ -6405,38 +6425,42 @@
       </c>
       <c r="V15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>119</v>
+      </c>
       <c r="D16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E16" s="5">
+        <v>138</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="3"/>
@@ -6444,14 +6468,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="11"/>
@@ -6459,14 +6483,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="13"/>
@@ -6474,38 +6498,42 @@
       </c>
       <c r="V16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>119</v>
+      </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E17" s="5">
+        <v>138</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6513,14 +6541,14 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6528,14 +6556,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6543,38 +6571,40 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>119</v>
+      </c>
       <c r="D18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="3"/>
@@ -6582,14 +6612,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="11"/>
@@ -6597,14 +6627,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="13"/>
@@ -6612,38 +6642,42 @@
       </c>
       <c r="V18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>119</v>
+      </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E19" s="5">
+        <v>138</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6651,14 +6685,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -6666,14 +6700,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6681,38 +6715,42 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="C20" s="1">
+        <v>119</v>
+      </c>
       <c r="D20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E20" s="5">
+        <v>138</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
@@ -6720,14 +6758,14 @@
       </c>
       <c r="J20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O20" s="5">
         <f t="shared" si="11"/>
@@ -6735,14 +6773,14 @@
       </c>
       <c r="P20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="13"/>
@@ -6750,38 +6788,40 @@
       </c>
       <c r="V20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>119</v>
+      </c>
       <c r="D21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
@@ -6789,14 +6829,14 @@
       </c>
       <c r="J21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O21" s="5">
         <f t="shared" si="11"/>
@@ -6804,14 +6844,14 @@
       </c>
       <c r="P21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U21" s="5">
         <f t="shared" si="13"/>
@@ -6819,14 +6859,14 @@
       </c>
       <c r="V21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="15"/>
@@ -6847,24 +6887,26 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1">
+        <v>133</v>
+      </c>
       <c r="D23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="3"/>
@@ -6872,14 +6914,14 @@
       </c>
       <c r="J23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O23" s="5">
         <f t="shared" si="11"/>
@@ -6887,14 +6929,14 @@
       </c>
       <c r="P23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="13"/>
@@ -6902,38 +6944,40 @@
       </c>
       <c r="V23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1">
+        <v>133</v>
+      </c>
       <c r="D24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="3"/>
@@ -6941,14 +6985,14 @@
       </c>
       <c r="J24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O24" s="5">
         <f t="shared" si="11"/>
@@ -6956,14 +7000,14 @@
       </c>
       <c r="P24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U24" s="5">
         <f t="shared" si="13"/>
@@ -6971,38 +7015,42 @@
       </c>
       <c r="V24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1">
+        <v>133</v>
+      </c>
       <c r="D25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="5"/>
+        <v>1064</v>
+      </c>
+      <c r="E25" s="5">
+        <v>148</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="3"/>
@@ -7010,14 +7058,14 @@
       </c>
       <c r="J25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" si="11"/>
@@ -7025,14 +7073,14 @@
       </c>
       <c r="P25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="13"/>
@@ -7040,38 +7088,42 @@
       </c>
       <c r="V25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W25" s="5"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1">
+        <v>133</v>
+      </c>
       <c r="D26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>1064</v>
+      </c>
+      <c r="E26" s="5">
+        <v>148</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="3"/>
@@ -7079,14 +7131,14 @@
       </c>
       <c r="J26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O26" s="5">
         <f t="shared" si="11"/>
@@ -7094,14 +7146,14 @@
       </c>
       <c r="P26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U26" s="5">
         <f t="shared" si="13"/>
@@ -7109,33 +7161,37 @@
       </c>
       <c r="V26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1">
+        <v>13</v>
+      </c>
       <c r="D27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="E27" s="5">
+        <v>148</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -7144,18 +7200,18 @@
       </c>
       <c r="I27" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="O27" s="5">
         <f t="shared" si="11"/>
@@ -7163,14 +7219,14 @@
       </c>
       <c r="P27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="U27" s="5">
         <f t="shared" si="13"/>
@@ -7178,38 +7234,42 @@
       </c>
       <c r="V27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="W27" s="5"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>133</v>
+      </c>
       <c r="D28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="5"/>
+        <v>1064</v>
+      </c>
+      <c r="E28" s="5">
+        <v>138</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="3"/>
@@ -7217,14 +7277,14 @@
       </c>
       <c r="J28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O28" s="5">
         <f t="shared" si="11"/>
@@ -7232,14 +7292,14 @@
       </c>
       <c r="P28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U28" s="5">
         <f t="shared" si="13"/>
@@ -7247,38 +7307,42 @@
       </c>
       <c r="V28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W28" s="5"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1">
+        <v>133</v>
+      </c>
       <c r="D29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="5"/>
+        <v>1064</v>
+      </c>
+      <c r="E29" s="5">
+        <v>148</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -7286,14 +7350,14 @@
       </c>
       <c r="J29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O29" s="5">
         <f t="shared" si="11"/>
@@ -7301,14 +7365,14 @@
       </c>
       <c r="P29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U29" s="5">
         <f t="shared" si="13"/>
@@ -7316,38 +7380,42 @@
       </c>
       <c r="V29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="1"/>
+      <c r="C30" s="1">
+        <v>133</v>
+      </c>
       <c r="D30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="5"/>
+        <v>1064</v>
+      </c>
+      <c r="E30" s="5">
+        <v>148</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
@@ -7355,14 +7423,14 @@
       </c>
       <c r="J30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O30" s="5">
         <f t="shared" si="11"/>
@@ -7370,14 +7438,14 @@
       </c>
       <c r="P30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" si="13"/>
@@ -7385,38 +7453,40 @@
       </c>
       <c r="V30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W30" s="5"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>133</v>
+      </c>
       <c r="D31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
         <f>IF((D31-E31)&lt;0,0,(D31-E31))</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="I31" s="5">
         <f>IF((E31-D31)&lt;0,0,(E31-D31))</f>
@@ -7424,14 +7494,14 @@
       </c>
       <c r="J31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="O31" s="5">
         <f t="shared" si="11"/>
@@ -7439,14 +7509,14 @@
       </c>
       <c r="P31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="U31" s="5">
         <f t="shared" si="13"/>
@@ -7454,14 +7524,14 @@
       </c>
       <c r="V31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1064</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="15"/>
@@ -7482,24 +7552,26 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>132</v>
+      </c>
       <c r="D33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="3"/>
@@ -7507,14 +7579,14 @@
       </c>
       <c r="J33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O33" s="5">
         <f t="shared" si="11"/>
@@ -7522,14 +7594,14 @@
       </c>
       <c r="P33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U33" s="5">
         <f t="shared" si="13"/>
@@ -7537,38 +7609,40 @@
       </c>
       <c r="V33" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W33" s="5"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>132</v>
+      </c>
       <c r="D34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="3"/>
@@ -7576,14 +7650,14 @@
       </c>
       <c r="J34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O34" s="5">
         <f t="shared" si="11"/>
@@ -7591,14 +7665,14 @@
       </c>
       <c r="P34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U34" s="5">
         <f t="shared" si="13"/>
@@ -7606,38 +7680,40 @@
       </c>
       <c r="V34" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W34" s="5"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA34" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1">
+        <v>132</v>
+      </c>
       <c r="D35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="3"/>
@@ -7645,14 +7721,14 @@
       </c>
       <c r="J35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O35" s="5">
         <f t="shared" si="11"/>
@@ -7660,14 +7736,14 @@
       </c>
       <c r="P35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U35" s="5">
         <f t="shared" si="13"/>
@@ -7675,38 +7751,40 @@
       </c>
       <c r="V35" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W35" s="5"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1">
+        <v>132</v>
+      </c>
       <c r="D36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="1"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="3"/>
@@ -7714,14 +7792,14 @@
       </c>
       <c r="J36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O36" s="5">
         <f t="shared" si="11"/>
@@ -7729,14 +7807,14 @@
       </c>
       <c r="P36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U36" s="5">
         <f t="shared" si="13"/>
@@ -7744,38 +7822,40 @@
       </c>
       <c r="V36" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W36" s="5"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="1"/>
+      <c r="C37" s="1">
+        <v>132</v>
+      </c>
       <c r="D37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="3"/>
@@ -7783,14 +7863,14 @@
       </c>
       <c r="J37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O37" s="5">
         <f t="shared" si="11"/>
@@ -7798,14 +7878,14 @@
       </c>
       <c r="P37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U37" s="5">
         <f t="shared" si="13"/>
@@ -7813,38 +7893,40 @@
       </c>
       <c r="V37" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W37" s="5"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1">
+        <v>132</v>
+      </c>
       <c r="D38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="1"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="3"/>
@@ -7852,14 +7934,14 @@
       </c>
       <c r="J38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O38" s="5">
         <f t="shared" si="11"/>
@@ -7867,14 +7949,14 @@
       </c>
       <c r="P38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U38" s="5">
         <f t="shared" si="13"/>
@@ -7882,38 +7964,40 @@
       </c>
       <c r="V38" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W38" s="5"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1">
+        <v>132</v>
+      </c>
       <c r="D39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="1"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="3"/>
@@ -7921,14 +8005,14 @@
       </c>
       <c r="J39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O39" s="5">
         <f t="shared" si="11"/>
@@ -7936,14 +8020,14 @@
       </c>
       <c r="P39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U39" s="5">
         <f t="shared" si="13"/>
@@ -7951,38 +8035,40 @@
       </c>
       <c r="V39" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W39" s="5"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA39" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="1"/>
+      <c r="C40" s="1">
+        <v>132</v>
+      </c>
       <c r="D40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="3"/>
@@ -7990,14 +8076,14 @@
       </c>
       <c r="J40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O40" s="5">
         <f t="shared" si="11"/>
@@ -8005,14 +8091,14 @@
       </c>
       <c r="P40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U40" s="5">
         <f t="shared" si="13"/>
@@ -8020,38 +8106,40 @@
       </c>
       <c r="V40" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W40" s="5"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>132</v>
+      </c>
       <c r="D41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="3"/>
@@ -8059,14 +8147,14 @@
       </c>
       <c r="J41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="O41" s="5">
         <f t="shared" si="11"/>
@@ -8074,14 +8162,14 @@
       </c>
       <c r="P41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="U41" s="5">
         <f t="shared" si="13"/>
@@ -8089,14 +8177,14 @@
       </c>
       <c r="V41" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="W41" s="5"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="15"/>
@@ -8117,24 +8205,28 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>119</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E43" s="5">
+        <v>119</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8142,14 +8234,14 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8157,14 +8249,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8172,38 +8264,42 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>119</v>
+      </c>
       <c r="D44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E44" s="5">
+        <v>119</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
@@ -8211,14 +8307,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="11"/>
@@ -8226,14 +8322,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="13"/>
@@ -8241,38 +8337,42 @@
       </c>
       <c r="V44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>119</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E45" s="5">
+        <v>119</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8280,14 +8380,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8295,14 +8395,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8310,38 +8410,42 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>119</v>
+      </c>
       <c r="D46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E46" s="5">
+        <v>119</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -8349,14 +8453,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="11"/>
@@ -8364,14 +8468,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="13"/>
@@ -8379,38 +8483,40 @@
       </c>
       <c r="V46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1">
+        <v>119</v>
+      </c>
       <c r="D47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="3"/>
@@ -8418,14 +8524,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="11"/>
@@ -8433,14 +8539,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="13"/>
@@ -8448,38 +8554,42 @@
       </c>
       <c r="V47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1">
+        <v>119</v>
+      </c>
       <c r="D48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E48" s="5">
+        <v>119</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
@@ -8487,14 +8597,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="11"/>
@@ -8502,14 +8612,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="13"/>
@@ -8517,38 +8627,40 @@
       </c>
       <c r="V48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1">
+        <v>119</v>
+      </c>
       <c r="D49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -8556,14 +8668,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -8571,14 +8683,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" si="13"/>
@@ -8586,38 +8698,42 @@
       </c>
       <c r="V49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA49" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1">
+        <v>119</v>
+      </c>
       <c r="D50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="E50" s="5">
+        <v>119</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
@@ -8625,14 +8741,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -8640,14 +8756,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="13"/>
@@ -8655,38 +8771,40 @@
       </c>
       <c r="V50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1">
+        <v>119</v>
+      </c>
       <c r="D51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
@@ -8694,14 +8812,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -8709,14 +8827,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="13"/>
@@ -8724,14 +8842,14 @@
       </c>
       <c r="V51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="15"/>
@@ -8752,24 +8870,26 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1">
+        <v>111</v>
+      </c>
       <c r="D53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="3"/>
@@ -8777,14 +8897,14 @@
       </c>
       <c r="J53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="11"/>
@@ -8792,14 +8912,14 @@
       </c>
       <c r="P53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="13"/>
@@ -8807,38 +8927,40 @@
       </c>
       <c r="V53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W53" s="5"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA53" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1">
+        <v>111</v>
+      </c>
       <c r="D54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="1"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
@@ -8846,14 +8968,14 @@
       </c>
       <c r="J54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O54" s="5">
         <f t="shared" si="11"/>
@@ -8861,14 +8983,14 @@
       </c>
       <c r="P54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" si="13"/>
@@ -8876,38 +8998,40 @@
       </c>
       <c r="V54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W54" s="5"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA54" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1">
+        <v>111</v>
+      </c>
       <c r="D55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="3"/>
@@ -8915,14 +9039,14 @@
       </c>
       <c r="J55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O55" s="5">
         <f t="shared" si="11"/>
@@ -8930,14 +9054,14 @@
       </c>
       <c r="P55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U55" s="5">
         <f t="shared" si="13"/>
@@ -8945,38 +9069,40 @@
       </c>
       <c r="V55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W55" s="5"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="1"/>
+      <c r="C56" s="1">
+        <v>111</v>
+      </c>
       <c r="D56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="3"/>
@@ -8984,14 +9110,14 @@
       </c>
       <c r="J56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O56" s="5">
         <f t="shared" si="11"/>
@@ -8999,14 +9125,14 @@
       </c>
       <c r="P56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" si="13"/>
@@ -9014,38 +9140,40 @@
       </c>
       <c r="V56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W56" s="5"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="1">
+        <v>111</v>
+      </c>
       <c r="D57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I57" s="5">
         <f t="shared" si="3"/>
@@ -9053,14 +9181,14 @@
       </c>
       <c r="J57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O57" s="5">
         <f t="shared" si="11"/>
@@ -9068,14 +9196,14 @@
       </c>
       <c r="P57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U57" s="5">
         <f t="shared" si="13"/>
@@ -9083,38 +9211,40 @@
       </c>
       <c r="V57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W57" s="5"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="1"/>
+      <c r="C58" s="1">
+        <v>111</v>
+      </c>
       <c r="D58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="3"/>
@@ -9122,14 +9252,14 @@
       </c>
       <c r="J58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="11"/>
@@ -9137,14 +9267,14 @@
       </c>
       <c r="P58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U58" s="5">
         <f t="shared" si="13"/>
@@ -9152,38 +9282,40 @@
       </c>
       <c r="V58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA58" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="1"/>
+      <c r="C59" s="1">
+        <v>111</v>
+      </c>
       <c r="D59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" si="3"/>
@@ -9191,14 +9323,14 @@
       </c>
       <c r="J59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O59" s="5">
         <f t="shared" si="11"/>
@@ -9206,14 +9338,14 @@
       </c>
       <c r="P59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U59" s="5">
         <f t="shared" si="13"/>
@@ -9221,38 +9353,40 @@
       </c>
       <c r="V59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W59" s="5"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1">
+        <v>111</v>
+      </c>
       <c r="D60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="3"/>
@@ -9260,14 +9394,14 @@
       </c>
       <c r="J60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O60" s="5">
         <f t="shared" si="11"/>
@@ -9275,14 +9409,14 @@
       </c>
       <c r="P60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" si="13"/>
@@ -9290,38 +9424,40 @@
       </c>
       <c r="V60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W60" s="5"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="1">
+        <v>111</v>
+      </c>
       <c r="D61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="3"/>
@@ -9329,14 +9465,14 @@
       </c>
       <c r="J61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="O61" s="5">
         <f t="shared" si="11"/>
@@ -9344,14 +9480,14 @@
       </c>
       <c r="P61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" si="13"/>
@@ -9359,14 +9495,14 @@
       </c>
       <c r="V61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="W61" s="5"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="AA61" s="5">
         <f t="shared" si="15"/>
@@ -14850,12 +14986,14 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>952</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>154</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f>IF((D18-E18)&lt;0,0,(D18-E18))</f>
-        <v>952</v>
+        <v>798</v>
       </c>
       <c r="I18" s="5">
         <f>IF((E18-D18)&lt;0,0,(E18-D18))</f>
